--- a/event_registration_forms/018_equipment_condition_monitoring_workshop_registration--event_registration_forms.xlsx
+++ b/event_registration_forms/018_equipment_condition_monitoring_workshop_registration--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'january'}</t>
+          <t>january</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'January'}</t>
+          <t>January</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'february'}</t>
+          <t>february</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'February'}</t>
+          <t>February</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'march'}</t>
+          <t>march</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'March'}</t>
+          <t>March</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'april'}</t>
+          <t>april</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'April'}</t>
+          <t>April</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'may'}</t>
+          <t>may</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'May'}</t>
+          <t>May</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'june'}</t>
+          <t>june</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'June'}</t>
+          <t>June</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'july'}</t>
+          <t>july</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'July'}</t>
+          <t>July</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'august'}</t>
+          <t>august</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'August'}</t>
+          <t>August</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'september'}</t>
+          <t>september</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'September'}</t>
+          <t>September</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'october'}</t>
+          <t>october</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'October'}</t>
+          <t>October</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'november'}</t>
+          <t>november</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'November'}</t>
+          <t>November</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'december'}</t>
+          <t>december</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'December'}</t>
+          <t>December</t>
         </is>
       </c>
     </row>
